--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,26 +47,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -167,19 +161,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,7 +796,7 @@
         <v>351.3</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>22.7</v>
@@ -814,9 +814,9 @@
         <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K4" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
@@ -826,13 +826,13 @@
         <v>22.7</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>98.2</v>
+        <v>97.5</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>33</v>
@@ -901,23 +901,23 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>-1.3</v>
+      <c r="M5" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q5" s="9" t="n">
         <v>26</v>
@@ -938,16 +938,16 @@
         <v>22</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>92</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>368</v>
+        <v>2368</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>31.4</v>
@@ -974,8 +974,8 @@
       <c r="F6" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>20.3</v>
+      <c r="G6" s="9" t="n">
+        <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
@@ -984,9 +984,9 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K6" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="9" t="n">
@@ -996,28 +996,28 @@
         <v>21.3</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>98.2</v>
+        <v>97.3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>31.4</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>24.9</v>
+        <v>22.5</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>31.5</v>
+        <v>27.3</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>68.5</v>
+        <v>59.6</v>
       </c>
       <c r="U6" s="9" t="n">
-        <v>14.5</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>28.3</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8218.200000000001</v>
+        <v>418.2</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>32.4</v>
@@ -1063,16 +1063,16 @@
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>21.1</v>
@@ -1081,13 +1081,13 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>31.9</v>
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>368</v>
+        <v>2368</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>33.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>27.5</v>
@@ -1151,12 +1151,12 @@
         <v>20.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
@@ -1166,43 +1166,43 @@
         <v>21.7</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>97.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>33.3</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>25.6</v>
+        <v>22.9</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>32.8</v>
+        <v>27.9</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>64.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>18.4</v>
+        <v>23</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>28.1</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>28.2</v>
+        <v>30.6</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>74.2</v>
+        <v>80.3</v>
       </c>
       <c r="Z8" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783</v>
+        <v>1783.6</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>161.7</v>
@@ -1229,8 +1229,8 @@
       <c r="F9" s="9" t="n">
         <v>134.5</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>5.4</v>
+      <c r="G9" s="9" t="n">
+        <v>54.3</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>100.8</v>
@@ -1241,32 +1241,32 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="16" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="15" t="n">
+      <c r="M9" s="16" t="n">
         <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>12.8</v>
+        <v>128.2</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q9" s="15" t="n">
-        <v>8556.6</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q9" s="16" t="n">
+        <v>255.6</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.5</v>
+        <v>137.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>308</v>
@@ -1274,20 +1274,20 @@
       <c r="U9" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="V9" s="15" t="n">
-        <v>32.7</v>
+      <c r="V9" s="9" t="n">
+        <v>135.7</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="X9" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>389.1</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>41.8</v>
+      <c r="X9" s="9" t="n">
+        <v>2087.1</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="Z9" s="9" t="n">
+        <v>1320</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>256.7</v>
+        <v>356.7</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>32.3</v>
@@ -1318,31 +1318,31 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L10" s="15" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="M10" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M10" s="16" t="n">
         <v>21.6</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>31.1</v>
@@ -1399,20 +1399,20 @@
       <c r="F11" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>18.7</v>
+      <c r="G11" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>88.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>18.1</v>
+        <v>14.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>20.6</v>
@@ -1433,31 +1433,31 @@
         <v>33.2</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>25.8</v>
+        <v>23.2</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>33.2</v>
+        <v>28.5</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>65.2</v>
+        <v>56.3</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>17.7</v>
+        <v>22.1</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>29.5</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>25.1</v>
+        <v>23.5</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>31.9</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>77.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>9.4</v>
+        <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1218.2</v>
+        <v>2418.2</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32.8</v>
@@ -1487,16 +1487,16 @@
       <c r="G12" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="18" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="9" t="n">
@@ -1532,17 +1532,17 @@
       <c r="V12" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>8.699999999999999</v>
+      <c r="X12" s="18" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>238.1</v>
+        <v>230.1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>24.9</v>
@@ -1576,12 +1576,12 @@
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="L13" s="9" t="n">
@@ -1617,17 +1617,17 @@
       <c r="V13" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X13" s="9" t="n">
+      <c r="W13" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="3" t="n">
         <v>80.8</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>6.6</v>
+      <c r="Z13" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1643,22 +1643,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1221.4</v>
+        <v>121.4</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="17" t="n">
-        <v>87.8</v>
+      <c r="H14" s="18" t="n">
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
@@ -1666,7 +1666,7 @@
       <c r="J14" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
@@ -1702,17 +1702,17 @@
       <c r="V14" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X14" s="9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>3.8</v>
+      <c r="X14" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>340.8</v>
+        <v>2340.8</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>12.1</v>
@@ -1749,9 +1749,9 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
@@ -1813,22 +1813,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>15308.1</v>
+        <v>1530.8</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>154.2</v>
       </c>
-      <c r="E16" s="15" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="E16" s="9" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="G16" s="9" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>1192.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1836,44 +1836,44 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="15" t="n">
+      <c r="K16" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="L16" s="15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M16" s="15" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>111.9</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>490</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>2.2</v>
+      <c r="L16" s="9" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>41.1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="15" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>331</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="V16" s="15" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W16" s="15" t="n">
-        <v>212</v>
+      <c r="R16" s="9" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>2505.6</v>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>2993</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="W16" s="16" t="n">
+        <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>140</v>
@@ -1882,7 +1882,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4.2</v>
+        <v>142.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1898,18 +1898,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>306.2</v>
+        <v>230.6</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="G17" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G17" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1922,7 +1922,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>20.6</v>
@@ -1957,17 +1957,17 @@
       <c r="V17" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="16" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="Z17" s="9" t="n">
-        <v>6.3</v>
+      <c r="X17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3341.1</v>
+        <v>33.2</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>19.2</v>
@@ -1998,13 +1998,13 @@
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
@@ -2012,17 +2012,17 @@
       <c r="L18" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="18" t="n">
         <v>19.4</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="18" t="n">
         <v>22.3</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="P18" s="9" t="n">
-        <v>0.7</v>
+      <c r="P18" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>32.2</v>
@@ -2043,16 +2043,16 @@
         <v>28.3</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X18" s="9" t="n">
-        <v>29.8</v>
+        <v>31.9</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>77.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="Z18" s="9" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.2</v>
+        <v>32.6</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>32.2</v>
@@ -2094,19 +2094,19 @@
       <c r="K19" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="O19" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="O19" s="9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P19" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="Q19" s="9" t="n">
@@ -2167,8 +2167,8 @@
       <c r="G20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="17" t="n">
-        <v>18.4</v>
+      <c r="H20" s="18" t="n">
+        <v>118.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>11.8</v>
@@ -2183,7 +2183,7 @@
         <v>19.8</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N20" s="9" t="n">
         <v>22.8</v>
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>357.5</v>
+        <v>35.7</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>30.1</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>24.1</v>
@@ -2252,7 +2252,7 @@
       <c r="G21" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="18" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2264,19 +2264,19 @@
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="16" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="N21" s="3" t="n">
+      <c r="M21" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="O21" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
@@ -2298,16 +2298,16 @@
         <v>26.3</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="X21" s="9" t="n">
-        <v>28.8</v>
+        <v>30.2</v>
       </c>
       <c r="Y21" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="Z21" s="9" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1492.9</v>
+        <v>294.9</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>31.2</v>
@@ -2337,8 +2337,8 @@
       <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="H22" s="17" t="n">
-        <v>17.4</v>
+      <c r="H22" s="18" t="n">
+        <v>167.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>11.9</v>
@@ -2364,35 +2364,35 @@
       <c r="P22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="n">
-        <v>21</v>
+      <c r="Q22" s="9" t="n">
+        <v>31</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>4.8</v>
+      <c r="S22" s="9" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>11.7</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>24</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="X22" s="9" t="n">
-        <v>26.5</v>
+        <v>27.4</v>
       </c>
       <c r="Y22" s="9" t="n">
-        <v>88.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1610.1</v>
+        <v>161</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="15" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>225.8</v>
-      </c>
-      <c r="G23" s="3" t="n">
+      <c r="E23" s="9" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="G23" s="9" t="n">
         <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.8</v>
+        <v>88.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2434,14 +2434,14 @@
       <c r="K23" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="15" t="n">
+      <c r="L23" s="9" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="15" t="n">
+      <c r="M23" s="16" t="n">
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12.2</v>
+        <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
@@ -2449,35 +2449,35 @@
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="15" t="n">
+      <c r="Q23" s="9" t="n">
         <v>152.9</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>124.6</v>
       </c>
-      <c r="S23" s="3" t="n">
-        <v>1139.7</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>795.1</v>
-      </c>
-      <c r="V23" s="15" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="W23" s="15" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="Y23" s="3" t="n">
-        <v>422</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+      <c r="S23" s="9" t="n">
+        <v>2419.8</v>
+      </c>
+      <c r="T23" s="9" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>3154.6</v>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="X23" s="9" t="n">
+        <v>2013.5</v>
+      </c>
+      <c r="Y23" s="9" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Z23" s="9" t="n">
+        <v>790.6</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>380.3</v>
+        <v>322</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>31.1</v>
@@ -2513,54 +2513,56 @@
       <c r="I24" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
+        <v>3.7</v>
+      </c>
       <c r="K24" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L24" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="15" t="n">
+      <c r="M24" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="O24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P24" s="3" t="n">
+      <c r="O24" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P24" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="15" t="n">
+      <c r="Q24" s="9" t="n">
         <v>30.6</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V24" s="9" t="n">
-        <v>25.9</v>
+      <c r="S24" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V24" s="16" t="n">
+        <v>2.5</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="Y24" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Z24" s="9" t="n">
-        <v>3.9</v>
+      <c r="X24" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>5.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2579,10 +2581,10 @@
         <v>177.8</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>24.9</v>
@@ -2594,19 +2596,19 @@
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.4</v>
+        <v>11.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="16" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="M25" s="16" t="n">
-        <v>49.44</v>
+      <c r="L25" s="19" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2617,35 +2619,35 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>1.8</v>
+      <c r="S25" s="9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="V25" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="17" t="n">
+      <c r="W25" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+      <c r="X25" s="9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="Y25" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z25" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2675,16 +2677,16 @@
       <c r="G26" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="17" t="n">
+      <c r="H26" s="18" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K26" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
@@ -2694,25 +2696,27 @@
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>15.8</v>
+        <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="16" t="n">
-        <v>88.40000000000001</v>
+      <c r="P26" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>31.4</v>
       </c>
       <c r="R26" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T26" s="9" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="V26" s="9" t="n">
@@ -2747,27 +2751,27 @@
         <v>418.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>37</v>
+        <v>32.9</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H27" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H27" s="18" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1</v>
+        <v>13.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
@@ -2803,17 +2807,17 @@
       <c r="V27" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="16" t="n">
-        <v>65.51000000000001</v>
-      </c>
-      <c r="X27" s="17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>10.5</v>
+      <c r="W27" s="9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X27" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="Y27" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z27" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2829,21 +2833,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.3</v>
+        <v>282.4</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>33.8</v>
+        <v>32.6</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G28" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G28" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="H28" s="17" t="n">
+      <c r="H28" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2852,10 +2856,10 @@
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="18" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2888,17 +2892,17 @@
       <c r="V28" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>0.2</v>
+      <c r="X28" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="Y28" s="9" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="Z28" s="9" t="n">
+        <v>3.1</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2914,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>14</v>
+        <v>146.2</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>8.9</v>
@@ -2937,7 +2941,9 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="13" t="inlineStr"/>
+      <c r="K29" s="9" t="n">
+        <v>18.1</v>
+      </c>
       <c r="L29" s="9" t="n">
         <v>21.9</v>
       </c>
@@ -2953,35 +2959,35 @@
       <c r="P29" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="9" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S29" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="T29" s="3" t="n">
+      <c r="T29" s="9" t="n">
         <v>73.7</v>
       </c>
-      <c r="U29" s="17" t="n">
-        <v>7.3</v>
+      <c r="U29" s="9" t="n">
+        <v>10.3</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>25</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>25.9</v>
+        <v>27.4</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>81.8</v>
+        <v>86.5</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2996,39 +3002,41 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="15" t="n">
-        <v>351.5</v>
+      <c r="C30" s="3" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>1156.5</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="F30" s="15" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>56.8</v>
+      <c r="F30" s="16" t="n">
+        <v>128</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>25.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>922.8</v>
+        <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K30" s="15" t="n">
+        <v>1171.8</v>
+      </c>
+      <c r="K30" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M30" s="15" t="n">
-        <v>10.1</v>
+      <c r="L30" s="16" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M30" s="16" t="n">
+        <v>101.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>111.3</v>
+        <v>117.8</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>489.5</v>
@@ -3036,35 +3044,35 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="15" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="R30" s="15" t="n">
-        <v>122</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>344.5</v>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>68.8</v>
+      <c r="Q30" s="9" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="S30" s="9" t="n">
+        <v>2156</v>
+      </c>
+      <c r="T30" s="9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>2378.5</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="9" t="n">
         <v>115.3</v>
       </c>
-      <c r="X30" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>411.5</v>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v>30.9</v>
+      <c r="X30" s="9" t="n">
+        <v>1787.4</v>
+      </c>
+      <c r="Y30" s="9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="Z30" s="9" t="n">
+        <v>855.7</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3091,7 +3099,9 @@
       <c r="F31" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
+      <c r="G31" s="9" t="n">
+        <v>11.4</v>
+      </c>
       <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
@@ -3099,53 +3109,55 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="16" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="16" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="O31" s="9" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P31" s="9" t="n">
+      <c r="O31" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="15" t="n">
+      <c r="Q31" s="9" t="n">
         <v>29.1</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="U31" s="17" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="V31" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W31" s="15" t="n">
+      <c r="S31" s="9" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="V31" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W31" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="17" t="n">
+      <c r="X31" s="18" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>82.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3175,14 +3187,14 @@
       <c r="G32" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="18" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
@@ -3197,7 +3209,7 @@
         <v>25.6</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>0.2</v>
@@ -3221,16 +3233,16 @@
         <v>27.1</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="X32" s="9" t="n">
-        <v>29.1</v>
+        <v>31.5</v>
       </c>
       <c r="Y32" s="9" t="n">
-        <v>81.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3246,7 +3258,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>48.1</v>
+        <v>44.1</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>25.2</v>
@@ -3264,13 +3276,13 @@
         <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K33" s="17" t="n">
-        <v>22.5</v>
+        <v>0.3</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>20.8</v>
@@ -3279,43 +3291,43 @@
         <v>20.6</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>25.2</v>
+        <v>26.6</v>
       </c>
       <c r="T33" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="U33" s="9" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="V33" s="9" t="n">
         <v>23</v>
       </c>
       <c r="W33" s="9" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="Y33" s="9" t="n">
-        <v>91.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Z33" s="9" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3345,14 +3357,14 @@
       <c r="G34" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H34" s="18" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>5.9</v>
@@ -3430,7 +3442,7 @@
       <c r="G35" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="17" t="n">
+      <c r="H35" s="18" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3443,49 +3455,49 @@
         <v>2.8</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N35" s="17" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O35" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="O35" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="P35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+      <c r="P35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>28.3</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>9.4</v>
+      <c r="S35" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="V35" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="17" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+      <c r="X35" s="9" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>3.7</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3501,7 +3513,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>117.2</v>
+        <v>1117.2</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>28.6</v>
@@ -3513,10 +3525,10 @@
         <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>19</v>
+        <v>17.5</v>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>119</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3525,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>21.9</v>
@@ -3537,38 +3549,40 @@
         <v>25.9</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q36" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S36" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="9" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="3" t="inlineStr"/>
+      <c r="U36" s="9" t="n">
+        <v>1.3</v>
+      </c>
       <c r="V36" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="16" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>19.3</v>
+      <c r="W36" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X36" s="9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3589,14 +3603,14 @@
       <c r="D37" s="9" t="n">
         <v>142.9</v>
       </c>
-      <c r="E37" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>42.9</v>
+      <c r="E37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>14.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3605,49 +3619,49 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K37" s="15" t="n">
-        <v>1807.9</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K37" s="16" t="n">
+        <v>17.9</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="15" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="15" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="R37" s="15" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>3923.6</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V37" s="15" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="W37" s="15" t="n">
-        <v>112.2</v>
+      <c r="M37" s="9" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="R37" s="9" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="S37" s="9" t="n">
+        <v>1948.4</v>
+      </c>
+      <c r="T37" s="9" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="V37" s="9" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="W37" s="16" t="n">
+        <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>12.2</v>
+        <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>416</v>
@@ -3669,7 +3683,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>165.3</v>
+        <v>16.5</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>28.6</v>
@@ -3683,17 +3697,17 @@
       <c r="G38" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="18" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>20.7</v>
@@ -3710,35 +3724,35 @@
       <c r="P38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="15" t="n">
-        <v>56.6</v>
+      <c r="Q38" s="9" t="n">
+        <v>26.6</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="V38" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W38" s="15" t="n">
+      <c r="S38" s="9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V38" s="16" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W38" s="9" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.2</v>
+        <v>183.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3754,7 +3768,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>33.2</v>
+        <v>332.3</v>
       </c>
       <c r="D39" s="9" t="n">
         <v>30.7</v>
@@ -3772,58 +3786,58 @@
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K39" s="3" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="P39" s="9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>30.7</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>23.7</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>29.3</v>
+        <v>32.6</v>
       </c>
       <c r="T39" s="9" t="n">
-        <v>66.5</v>
+        <v>73.8</v>
       </c>
       <c r="U39" s="9" t="n">
-        <v>14.7</v>
+        <v>11.6</v>
       </c>
       <c r="V39" s="9" t="n">
         <v>27.8</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>22.5</v>
+        <v>23.9</v>
       </c>
       <c r="X39" s="9" t="n">
-        <v>27.2</v>
+        <v>29.7</v>
       </c>
       <c r="Y39" s="9" t="n">
-        <v>72.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="Z39" s="9" t="n">
-        <v>10.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3839,13 +3853,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2728.1</v>
+        <v>278.1</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>30.8</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>20.6</v>
+        <v>20.06</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>25.7</v>
@@ -3869,13 +3883,13 @@
         <v>21</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>0.2</v>
@@ -3884,16 +3898,16 @@
         <v>30.7</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>28.8</v>
+        <v>32.2</v>
       </c>
       <c r="T40" s="9" t="n">
-        <v>65.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="U40" s="9" t="n">
-        <v>15.2</v>
+        <v>11.9</v>
       </c>
       <c r="V40" s="9" t="n">
         <v>28</v>
@@ -3942,11 +3956,9 @@
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
         <v>11.8</v>
       </c>
@@ -3965,20 +3977,20 @@
       <c r="P41" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="9" t="n">
         <v>29.3</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>12</v>
+      <c r="S41" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="V41" s="9" t="n">
         <v>27.1</v>
@@ -4038,17 +4050,17 @@
       <c r="L42" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="17" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
+      <c r="M42" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="O42" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="P42" s="3" t="n">
-        <v>80.8</v>
+      <c r="P42" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>30.9</v>
@@ -4105,14 +4117,14 @@
       <c r="F43" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>18.6</v>
+      <c r="G43" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H43" s="18" t="n">
+        <v>8.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21.6</v>
+        <v>41.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4130,25 +4142,25 @@
         <v>25</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S43" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S43" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="T43" s="3" t="n">
+      <c r="T43" s="9" t="n">
         <v>77</v>
       </c>
-      <c r="U43" s="3" t="n">
-        <v>2.1</v>
+      <c r="U43" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="V43" s="9" t="n">
         <v>24</v>
@@ -4183,18 +4195,18 @@
       </c>
       <c r="D44" s="9" t="inlineStr"/>
       <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="13" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
       <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4220,72 +4232,74 @@
       <c r="C45" s="3" t="n">
         <v>1423.4</v>
       </c>
-      <c r="D45" s="15" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="G45" s="16" t="n">
+      <c r="D45" s="16" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>802.1</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>1127.8</v>
+      </c>
+      <c r="G45" s="19" t="n">
         <v>19.1</v>
       </c>
       <c r="H45" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I45" s="3" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="I45" s="3" t="n">
-        <v>82.5</v>
-      </c>
       <c r="J45" s="3" t="n">
-        <v>1814.9</v>
-      </c>
-      <c r="K45" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="L45" s="15" t="n">
-        <v>105081.6</v>
-      </c>
-      <c r="M45" s="14" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K45" s="16" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="M45" s="16" t="n">
+        <v>102.9</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>1820.5</v>
+        <v>120.5</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q45" s="15" t="n">
-        <v>846.3</v>
-      </c>
-      <c r="R45" s="15" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>341.4</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="V45" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="W45" s="15" t="n">
-        <v>112.8</v>
+        <v>11.9</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="R45" s="9" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="S45" s="9" t="n">
+        <v>2248.4</v>
+      </c>
+      <c r="T45" s="9" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>2390.2</v>
+      </c>
+      <c r="V45" s="16" t="n">
+        <v>1234</v>
+      </c>
+      <c r="W45" s="16" t="n">
+        <v>219</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>12.2</v>
+        <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>9929.5</v>
+        <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>80.5</v>
+        <v>5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4312,11 +4326,11 @@
       <c r="F46" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="17" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H46" s="17" t="n">
-        <v>88.7</v>
+      <c r="G46" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>11.7</v>
@@ -4325,13 +4339,13 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N46" s="9" t="n">
         <v>24.1</v>
@@ -4342,11 +4356,11 @@
       <c r="P46" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="15" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="R46" s="9" t="n">
-        <v>24.5</v>
+      <c r="Q46" s="9" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R46" s="16" t="n">
+        <v>2.4</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>27.8</v>
